--- a/Caleb_2026.xlsx
+++ b/Caleb_2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="26">
   <si>
     <t>月份</t>
   </si>
@@ -1020,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -1174,6 +1174,12 @@
       <c r="I4" t="s">
         <v>9</v>
       </c>
+      <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1194,6 +1200,12 @@
       <c r="I5" t="s">
         <v>9</v>
       </c>
+      <c r="K5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1211,6 +1223,12 @@
       <c r="I6" t="s">
         <v>9</v>
       </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1231,6 +1249,12 @@
       <c r="I7" t="s">
         <v>9</v>
       </c>
+      <c r="K7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1262,6 +1286,12 @@
       <c r="I9" t="s">
         <v>9</v>
       </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1282,6 +1312,12 @@
       <c r="I10" t="s">
         <v>9</v>
       </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1293,6 +1329,12 @@
       <c r="I11" t="s">
         <v>9</v>
       </c>
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1301,6 +1343,12 @@
       <c r="E12" t="s">
         <v>9</v>
       </c>
+      <c r="M12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1318,6 +1366,18 @@
       <c r="I13" t="s">
         <v>9</v>
       </c>
+      <c r="K13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1332,23 +1392,41 @@
       <c r="H14" t="s">
         <v>9</v>
       </c>
+      <c r="M14" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1361,15 +1439,35 @@
       <c r="I18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>9</v>
+      </c>
+      <c r="N19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>9</v>
+      </c>
+      <c r="N21" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Caleb_2026.xlsx
+++ b/Caleb_2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="26">
   <si>
     <t>月份</t>
   </si>
@@ -1180,6 +1180,12 @@
       <c r="L4" t="s">
         <v>9</v>
       </c>
+      <c r="M4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1206,6 +1212,12 @@
       <c r="L5" t="s">
         <v>9</v>
       </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1229,6 +1241,12 @@
       <c r="L6" t="s">
         <v>9</v>
       </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1253,6 +1271,12 @@
         <v>9</v>
       </c>
       <c r="L7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Caleb_2026.xlsx
+++ b/Caleb_2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="26">
   <si>
     <t>月份</t>
   </si>
@@ -1347,6 +1347,9 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
@@ -1378,6 +1381,9 @@
       <c r="A13" t="s">
         <v>18</v>
       </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
@@ -1427,6 +1433,9 @@
       <c r="A15" t="s">
         <v>20</v>
       </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
       <c r="M15" t="s">
         <v>9</v>
       </c>
@@ -1438,6 +1447,9 @@
       <c r="A16" t="s">
         <v>21</v>
       </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1454,6 +1466,9 @@
       <c r="A18" t="s">
         <v>23</v>
       </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
@@ -1484,6 +1499,9 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
